--- a/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_py_2021_2025.xlsx
+++ b/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_py_2021_2025.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>28-01-2021 08:30</t>
+          <t>2021-01-28 08:30:00</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -812,7 +812,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -905,7 +905,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -998,7 +998,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T6" t="n">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T7" t="n">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>02-12-2021 08:30</t>
+          <t>2021-02-12 08:30:00</t>
         </is>
       </c>
       <c r="T8" t="n">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T9" t="n">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T10" t="n">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>06-09-2021 08:30</t>
+          <t>2021-06-09 08:30:00</t>
         </is>
       </c>
       <c r="T11" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>02-12-2021 08:30</t>
+          <t>2021-02-12 08:30:00</t>
         </is>
       </c>
       <c r="T12" t="n">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T13" t="n">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>06-09-2021 08:30</t>
+          <t>2021-06-09 08:30:00</t>
         </is>
       </c>
       <c r="T14" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T15" t="n">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>13-09-2021 08:30</t>
+          <t>2021-09-13 08:30:00</t>
         </is>
       </c>
       <c r="T16" t="n">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T17" t="n">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>13-09-2021 08:30</t>
+          <t>2021-09-13 08:30:00</t>
         </is>
       </c>
       <c r="T18" t="n">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T19" t="n">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>06-09-2021 08:30</t>
+          <t>2021-06-09 08:30:00</t>
         </is>
       </c>
       <c r="T20" t="n">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T21" t="n">
@@ -2558,7 +2558,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>15-09-2021 08:30</t>
+          <t>2021-09-15 08:30:00</t>
         </is>
       </c>
       <c r="T22" t="n">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T23" t="n">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>06-09-2021 08:30</t>
+          <t>2021-06-09 08:30:00</t>
         </is>
       </c>
       <c r="T24" t="n">
@@ -2855,7 +2855,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T25" t="n">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>13-09-2021 08:30</t>
+          <t>2021-09-13 08:30:00</t>
         </is>
       </c>
       <c r="T26" t="n">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T27" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>13-09-2021 08:30</t>
+          <t>2021-09-13 08:30:00</t>
         </is>
       </c>
       <c r="T28" t="n">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T29" t="n">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>13-09-2021 08:30</t>
+          <t>2021-09-13 08:30:00</t>
         </is>
       </c>
       <c r="T30" t="n">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T31" t="n">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>13-09-2021 08:30</t>
+          <t>2021-09-13 08:30:00</t>
         </is>
       </c>
       <c r="T32" t="n">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T33" t="n">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>13-09-2021 08:30</t>
+          <t>2021-09-13 08:30:00</t>
         </is>
       </c>
       <c r="T34" t="n">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T35" t="n">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>06-09-2021 08:30</t>
+          <t>2021-06-09 08:30:00</t>
         </is>
       </c>
       <c r="T36" t="n">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>28-01-2021 08:30</t>
+          <t>2021-01-28 08:30:00</t>
         </is>
       </c>
       <c r="T37" t="n">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>15-09-2021 08:30</t>
+          <t>2021-09-15 08:30:00</t>
         </is>
       </c>
       <c r="T38" t="n">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T39" t="n">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>06-09-2021 08:30</t>
+          <t>2021-06-09 08:30:00</t>
         </is>
       </c>
       <c r="T40" t="n">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T41" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>06-09-2021 08:30</t>
+          <t>2021-06-09 08:30:00</t>
         </is>
       </c>
       <c r="T42" t="n">
